--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V327"/>
+  <dimension ref="A1:V328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23990,6 +23990,78 @@
       <c r="V327" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>364.7</v>
+      </c>
+      <c r="C328" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="D328" t="n">
+        <v>348.47</v>
+      </c>
+      <c r="E328" t="n">
+        <v>352.42</v>
+      </c>
+      <c r="F328" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="G328" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="H328" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="I328" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="J328" t="n">
+        <v>330.78</v>
+      </c>
+      <c r="K328" t="n">
+        <v>332.51</v>
+      </c>
+      <c r="L328" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="M328" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="N328" t="n">
+        <v>327.41</v>
+      </c>
+      <c r="O328" t="n">
+        <v>321.29</v>
+      </c>
+      <c r="P328" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="R328" t="n">
+        <v>338.52</v>
+      </c>
+      <c r="S328" t="n">
+        <v>338.62</v>
+      </c>
+      <c r="T328" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="U328" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27307,6 +27379,16 @@
       </c>
       <c r="B330" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -27475,28 +27557,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3947133547203725</v>
+        <v>-0.3930581670858305</v>
       </c>
       <c r="J2" t="n">
+        <v>327</v>
+      </c>
+      <c r="K2" t="n">
         <v>326</v>
       </c>
-      <c r="K2" t="n">
-        <v>325</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2715182386793363</v>
+        <v>0.2709583997566308</v>
       </c>
       <c r="M2" t="n">
-        <v>3.658967352456566</v>
+        <v>3.656042320193278</v>
       </c>
       <c r="N2" t="n">
-        <v>23.65898520095136</v>
+        <v>23.6100102894622</v>
       </c>
       <c r="O2" t="n">
-        <v>4.864050287666787</v>
+        <v>4.85901330410426</v>
       </c>
       <c r="P2" t="n">
-        <v>372.4910712994616</v>
+        <v>372.473447710192</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27553,28 +27635,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3394148554963347</v>
+        <v>-0.339719418563833</v>
       </c>
       <c r="J3" t="n">
+        <v>327</v>
+      </c>
+      <c r="K3" t="n">
         <v>326</v>
       </c>
-      <c r="K3" t="n">
-        <v>325</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1704042148801257</v>
+        <v>0.1715865694622868</v>
       </c>
       <c r="M3" t="n">
-        <v>4.471020327486012</v>
+        <v>4.458725987922581</v>
       </c>
       <c r="N3" t="n">
-        <v>31.74393006164398</v>
+        <v>31.64735504419797</v>
       </c>
       <c r="O3" t="n">
-        <v>5.634175189115438</v>
+        <v>5.625598194343245</v>
       </c>
       <c r="P3" t="n">
-        <v>358.2084686499819</v>
+        <v>358.2117114813661</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27631,28 +27713,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4017713402277486</v>
+        <v>-0.4014913172879236</v>
       </c>
       <c r="J4" t="n">
+        <v>327</v>
+      </c>
+      <c r="K4" t="n">
         <v>326</v>
       </c>
-      <c r="K4" t="n">
-        <v>325</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2208512832196421</v>
+        <v>0.2217399169828803</v>
       </c>
       <c r="M4" t="n">
-        <v>4.332760274993841</v>
+        <v>4.320857339986531</v>
       </c>
       <c r="N4" t="n">
-        <v>32.23228812012407</v>
+        <v>32.1340915003686</v>
       </c>
       <c r="O4" t="n">
-        <v>5.677348687558663</v>
+        <v>5.668693985422798</v>
       </c>
       <c r="P4" t="n">
-        <v>358.7658394691342</v>
+        <v>358.7628579284469</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27709,28 +27791,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4427042427961592</v>
+        <v>-0.4441484396729365</v>
       </c>
       <c r="J5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2235979261704557</v>
+        <v>0.2257948608086094</v>
       </c>
       <c r="M5" t="n">
-        <v>4.887896264462946</v>
+        <v>4.880292197834744</v>
       </c>
       <c r="N5" t="n">
-        <v>38.50509472009965</v>
+        <v>38.40459561466024</v>
       </c>
       <c r="O5" t="n">
-        <v>6.205247353659614</v>
+        <v>6.197144149901649</v>
       </c>
       <c r="P5" t="n">
-        <v>366.721117374815</v>
+        <v>366.7365156390775</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27787,28 +27869,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3511570832770056</v>
+        <v>-0.3496929534722496</v>
       </c>
       <c r="J6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1835405306634276</v>
+        <v>0.1831829751827884</v>
       </c>
       <c r="M6" t="n">
-        <v>4.429650724598465</v>
+        <v>4.422498383603676</v>
       </c>
       <c r="N6" t="n">
-        <v>31.03683487825739</v>
+        <v>30.95981472943318</v>
       </c>
       <c r="O6" t="n">
-        <v>5.57107125050985</v>
+        <v>5.564154448740005</v>
       </c>
       <c r="P6" t="n">
-        <v>362.0430148280598</v>
+        <v>362.027404035646</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27865,28 +27947,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3667296955655689</v>
+        <v>-0.3662112133627405</v>
       </c>
       <c r="J7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09550611842853685</v>
+        <v>0.09582772788520744</v>
       </c>
       <c r="M7" t="n">
-        <v>6.507989691851438</v>
+        <v>6.491165783983242</v>
       </c>
       <c r="N7" t="n">
-        <v>71.89404250458078</v>
+        <v>71.6764899001605</v>
       </c>
       <c r="O7" t="n">
-        <v>8.479035470180602</v>
+        <v>8.466196897081977</v>
       </c>
       <c r="P7" t="n">
-        <v>341.8376939558855</v>
+        <v>341.8321683023154</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27943,28 +28025,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.453785048964173</v>
+        <v>-0.4524710336446606</v>
       </c>
       <c r="J8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2085499424655491</v>
+        <v>0.2086229975554876</v>
       </c>
       <c r="M8" t="n">
-        <v>4.948355917467667</v>
+        <v>4.939710139558483</v>
       </c>
       <c r="N8" t="n">
-        <v>44.11031061639729</v>
+        <v>43.99023345273322</v>
       </c>
       <c r="O8" t="n">
-        <v>6.641559351266635</v>
+        <v>6.632513358654713</v>
       </c>
       <c r="P8" t="n">
-        <v>338.9099980565082</v>
+        <v>338.895994116929</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28021,28 +28103,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4538750143996267</v>
+        <v>-0.451556350903722</v>
       </c>
       <c r="J9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2281063191060153</v>
+        <v>0.227255315584491</v>
       </c>
       <c r="M9" t="n">
-        <v>4.803375457713761</v>
+        <v>4.799615064030725</v>
       </c>
       <c r="N9" t="n">
-        <v>39.34767087631887</v>
+        <v>39.27347629916861</v>
       </c>
       <c r="O9" t="n">
-        <v>6.27277218431523</v>
+        <v>6.266855375638456</v>
       </c>
       <c r="P9" t="n">
-        <v>341.5988551096402</v>
+        <v>341.5741442687399</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28099,28 +28181,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5352832800371294</v>
+        <v>-0.53563020755713</v>
       </c>
       <c r="J10" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K10" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3167524858262043</v>
+        <v>0.3184528049863707</v>
       </c>
       <c r="M10" t="n">
-        <v>4.587982351272403</v>
+        <v>4.575617405667268</v>
       </c>
       <c r="N10" t="n">
-        <v>34.88604158789069</v>
+        <v>34.78038927739696</v>
       </c>
       <c r="O10" t="n">
-        <v>5.906440686901942</v>
+        <v>5.897490082857025</v>
       </c>
       <c r="P10" t="n">
-        <v>345.7106372545236</v>
+        <v>345.7143345873906</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28177,28 +28259,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6490975307561974</v>
+        <v>-0.6469245812639257</v>
       </c>
       <c r="J11" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K11" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4567922197750252</v>
+        <v>0.4564043106226618</v>
       </c>
       <c r="M11" t="n">
-        <v>4.021142524578003</v>
+        <v>4.020129074511359</v>
       </c>
       <c r="N11" t="n">
-        <v>28.28091828464109</v>
+        <v>28.23495061653577</v>
       </c>
       <c r="O11" t="n">
-        <v>5.317980658543343</v>
+        <v>5.313656990861921</v>
       </c>
       <c r="P11" t="n">
-        <v>346.2591026758584</v>
+        <v>346.2359447621366</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28255,28 +28337,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6702909131509986</v>
+        <v>-0.6666654859104508</v>
       </c>
       <c r="J12" t="n">
+        <v>327</v>
+      </c>
+      <c r="K12" t="n">
         <v>326</v>
       </c>
-      <c r="K12" t="n">
-        <v>325</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.4477933201430208</v>
+        <v>0.4458508258398806</v>
       </c>
       <c r="M12" t="n">
-        <v>4.332847805443882</v>
+        <v>4.338550279226093</v>
       </c>
       <c r="N12" t="n">
-        <v>31.08209053470782</v>
+        <v>31.09862721387</v>
       </c>
       <c r="O12" t="n">
-        <v>5.575131436541009</v>
+        <v>5.576614314606131</v>
       </c>
       <c r="P12" t="n">
-        <v>350.4700572797154</v>
+        <v>350.4312284653547</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28333,28 +28415,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6860753648948783</v>
+        <v>-0.6825032015486743</v>
       </c>
       <c r="J13" t="n">
+        <v>327</v>
+      </c>
+      <c r="K13" t="n">
         <v>326</v>
       </c>
-      <c r="K13" t="n">
-        <v>325</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.4237192616612184</v>
+        <v>0.4220407664351912</v>
       </c>
       <c r="M13" t="n">
-        <v>4.712545125477602</v>
+        <v>4.714617127327269</v>
       </c>
       <c r="N13" t="n">
-        <v>35.91360981273456</v>
+        <v>35.91206258718864</v>
       </c>
       <c r="O13" t="n">
-        <v>5.992796493519078</v>
+        <v>5.992667401682547</v>
       </c>
       <c r="P13" t="n">
-        <v>348.7248807862337</v>
+        <v>348.6866224353601</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28411,28 +28493,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6530973223611656</v>
+        <v>-0.6511864494076315</v>
       </c>
       <c r="J14" t="n">
+        <v>327</v>
+      </c>
+      <c r="K14" t="n">
         <v>326</v>
       </c>
-      <c r="K14" t="n">
-        <v>325</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.430822648378964</v>
+        <v>0.4307603683539967</v>
       </c>
       <c r="M14" t="n">
-        <v>4.346610909289446</v>
+        <v>4.342041684317139</v>
       </c>
       <c r="N14" t="n">
-        <v>31.61290477313682</v>
+        <v>31.54701400996027</v>
       </c>
       <c r="O14" t="n">
-        <v>5.62253543991826</v>
+        <v>5.616672859439142</v>
       </c>
       <c r="P14" t="n">
-        <v>341.7165789561367</v>
+        <v>341.6961132492679</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28489,28 +28571,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6180947681035411</v>
+        <v>-0.6172769169177079</v>
       </c>
       <c r="J15" t="n">
+        <v>327</v>
+      </c>
+      <c r="K15" t="n">
         <v>326</v>
       </c>
-      <c r="K15" t="n">
-        <v>325</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.3967160554721634</v>
+        <v>0.3976183806449669</v>
       </c>
       <c r="M15" t="n">
-        <v>4.550017598403111</v>
+        <v>4.540590681513996</v>
       </c>
       <c r="N15" t="n">
-        <v>32.59204696959849</v>
+        <v>32.49776493515044</v>
       </c>
       <c r="O15" t="n">
-        <v>5.708944470705464</v>
+        <v>5.700681093970302</v>
       </c>
       <c r="P15" t="n">
-        <v>336.4890360740491</v>
+        <v>336.4802767776235</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28567,28 +28649,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5863233931803971</v>
+        <v>-0.5830602879751351</v>
       </c>
       <c r="J16" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K16" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L16" t="n">
-        <v>0.333030592119696</v>
+        <v>0.3314912401502534</v>
       </c>
       <c r="M16" t="n">
-        <v>5.005204084860642</v>
+        <v>5.007352933439043</v>
       </c>
       <c r="N16" t="n">
-        <v>38.86176654911869</v>
+        <v>38.83429547737806</v>
       </c>
       <c r="O16" t="n">
-        <v>6.233920640264736</v>
+        <v>6.231716896440182</v>
       </c>
       <c r="P16" t="n">
-        <v>343.9949548709098</v>
+        <v>343.9601787709234</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28645,28 +28727,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3772001835648608</v>
+        <v>-0.3733225379012092</v>
       </c>
       <c r="J17" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K17" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1746073682915443</v>
+        <v>0.1721009350131261</v>
       </c>
       <c r="M17" t="n">
-        <v>5.010047887106707</v>
+        <v>5.016164737806367</v>
       </c>
       <c r="N17" t="n">
-        <v>37.96366403161726</v>
+        <v>37.97659652144823</v>
       </c>
       <c r="O17" t="n">
-        <v>6.161466061873363</v>
+        <v>6.162515437826361</v>
       </c>
       <c r="P17" t="n">
-        <v>343.2191499681775</v>
+        <v>343.1778244868251</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28723,28 +28805,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4011231403261148</v>
+        <v>-0.3963547350169374</v>
       </c>
       <c r="J18" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K18" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2191993066985664</v>
+        <v>0.2152257354765243</v>
       </c>
       <c r="M18" t="n">
-        <v>4.638593054986422</v>
+        <v>4.652452949497109</v>
       </c>
       <c r="N18" t="n">
-        <v>32.35063106870774</v>
+        <v>32.44681799737642</v>
       </c>
       <c r="O18" t="n">
-        <v>5.687761516511372</v>
+        <v>5.696210845586426</v>
       </c>
       <c r="P18" t="n">
-        <v>341.247397209671</v>
+        <v>341.1965785785278</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28801,28 +28883,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4694141317287199</v>
+        <v>-0.4639622829533094</v>
       </c>
       <c r="J19" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K19" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3528568250058306</v>
+        <v>0.3465036485828491</v>
       </c>
       <c r="M19" t="n">
-        <v>3.809416323598367</v>
+        <v>3.830129237119674</v>
       </c>
       <c r="N19" t="n">
-        <v>22.81079820947406</v>
+        <v>22.99609890063171</v>
       </c>
       <c r="O19" t="n">
-        <v>4.77606513873859</v>
+        <v>4.795424788340624</v>
       </c>
       <c r="P19" t="n">
-        <v>342.0240696354168</v>
+        <v>341.9659672984714</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28879,28 +28961,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3432399835551086</v>
+        <v>-0.3409282708356152</v>
       </c>
       <c r="J20" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K20" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2391985611313676</v>
+        <v>0.2375448666773111</v>
       </c>
       <c r="M20" t="n">
-        <v>3.729230328508644</v>
+        <v>3.728502753189932</v>
       </c>
       <c r="N20" t="n">
-        <v>21.15119050849915</v>
+        <v>21.132366474233</v>
       </c>
       <c r="O20" t="n">
-        <v>4.599042346891268</v>
+        <v>4.596995374615141</v>
       </c>
       <c r="P20" t="n">
-        <v>349.2520364672171</v>
+        <v>349.2273997032711</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28957,28 +29039,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1731819400792628</v>
+        <v>-0.171475372768502</v>
       </c>
       <c r="J21" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K21" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0601141038425026</v>
+        <v>0.05931826499439974</v>
       </c>
       <c r="M21" t="n">
-        <v>3.874382769098083</v>
+        <v>3.873730211217965</v>
       </c>
       <c r="N21" t="n">
-        <v>26.46855704921724</v>
+        <v>26.412605334873</v>
       </c>
       <c r="O21" t="n">
-        <v>5.144760154683329</v>
+        <v>5.139319540062965</v>
       </c>
       <c r="P21" t="n">
-        <v>350.3352938818199</v>
+        <v>350.3171063727758</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29016,7 +29098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V327"/>
+  <dimension ref="A1:V328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65599,6 +65681,118 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-41.317434517250646,175.8627188880451</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-41.31788225162142,175.86201672509074</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-41.31838504990278,175.86141973495353</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-41.31888036934798,175.8608138042202</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-41.31942283201727,175.86028119083855</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-41.31975920086169,175.85946250881108</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-41.320153866214795,175.85874635602124</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-41.320599914059144,175.85808411364903</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-41.32095742596319,175.85733723686693</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-41.321312135279236,175.85659773579755</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-41.32163116614897,175.85582375613185</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-41.3218637636671,175.85498214284718</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-41.322041959192774,175.8541068922973</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-41.32223851446601,175.85326285261203</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-41.32252465608354,175.85244866282378</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>-41.322828474651146,175.85162989025642</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>-41.3231547710185,175.8508306028848</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>-41.32351850726789,175.85007555143125</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>-41.323880179814715,175.8493179817951</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>-41.32428870923772,175.84860360559574</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V328"/>
+  <dimension ref="A1:V330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24060,6 +24060,150 @@
         <v>348.56</v>
       </c>
       <c r="V328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:39+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>363.32</v>
+      </c>
+      <c r="C329" t="n">
+        <v>347.98</v>
+      </c>
+      <c r="D329" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="E329" t="n">
+        <v>351.31</v>
+      </c>
+      <c r="F329" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="G329" t="n">
+        <v>332.02</v>
+      </c>
+      <c r="H329" t="n">
+        <v>327.69</v>
+      </c>
+      <c r="I329" t="n">
+        <v>331.62</v>
+      </c>
+      <c r="J329" t="n">
+        <v>330.38</v>
+      </c>
+      <c r="K329" t="n">
+        <v>332.22</v>
+      </c>
+      <c r="L329" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="M329" t="n">
+        <v>335.07</v>
+      </c>
+      <c r="N329" t="n">
+        <v>326.91</v>
+      </c>
+      <c r="O329" t="n">
+        <v>320.66</v>
+      </c>
+      <c r="P329" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>338.07</v>
+      </c>
+      <c r="R329" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="S329" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="T329" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="U329" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>363.32</v>
+      </c>
+      <c r="C330" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="D330" t="n">
+        <v>347.47</v>
+      </c>
+      <c r="E330" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="F330" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="G330" t="n">
+        <v>331.88</v>
+      </c>
+      <c r="H330" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="I330" t="n">
+        <v>331.35</v>
+      </c>
+      <c r="J330" t="n">
+        <v>330.52</v>
+      </c>
+      <c r="K330" t="n">
+        <v>331.83</v>
+      </c>
+      <c r="L330" t="n">
+        <v>337.17</v>
+      </c>
+      <c r="M330" t="n">
+        <v>334.67</v>
+      </c>
+      <c r="N330" t="n">
+        <v>326.51</v>
+      </c>
+      <c r="O330" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="P330" t="n">
+        <v>332.99</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>338.52</v>
+      </c>
+      <c r="R330" t="n">
+        <v>337.13</v>
+      </c>
+      <c r="S330" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="T330" t="n">
+        <v>342.73</v>
+      </c>
+      <c r="U330" t="n">
+        <v>347.67</v>
+      </c>
+      <c r="V330" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24076,7 +24220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B331"/>
+  <dimension ref="A1:B333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27389,6 +27533,26 @@
       </c>
       <c r="B331" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>
@@ -27557,28 +27721,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3930581670858305</v>
+        <v>-0.3914144647597693</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2709583997566308</v>
+        <v>0.2717775279248571</v>
       </c>
       <c r="M2" t="n">
-        <v>3.656042320193278</v>
+        <v>3.641898587598087</v>
       </c>
       <c r="N2" t="n">
-        <v>23.6100102894622</v>
+        <v>23.47783227998589</v>
       </c>
       <c r="O2" t="n">
-        <v>4.85901330410426</v>
+        <v>4.84539289222101</v>
       </c>
       <c r="P2" t="n">
-        <v>372.473447710192</v>
+        <v>372.4559041459983</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27635,28 +27799,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.339719418563833</v>
+        <v>-0.3412527208725835</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1715865694622868</v>
+        <v>0.1746931339644026</v>
       </c>
       <c r="M3" t="n">
-        <v>4.458725987922581</v>
+        <v>4.438606112659891</v>
       </c>
       <c r="N3" t="n">
-        <v>31.64735504419797</v>
+        <v>31.46484442988869</v>
       </c>
       <c r="O3" t="n">
-        <v>5.625598194343245</v>
+        <v>5.609353298722473</v>
       </c>
       <c r="P3" t="n">
-        <v>358.2117114813661</v>
+        <v>358.2280799602715</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27713,28 +27877,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4014913172879236</v>
+        <v>-0.4020205160935634</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2217399169828803</v>
+        <v>0.2244475235343523</v>
       </c>
       <c r="M4" t="n">
-        <v>4.320857339986531</v>
+        <v>4.29732404206056</v>
       </c>
       <c r="N4" t="n">
-        <v>32.1340915003686</v>
+        <v>31.93938325468139</v>
       </c>
       <c r="O4" t="n">
-        <v>5.668693985422798</v>
+        <v>5.651493895836869</v>
       </c>
       <c r="P4" t="n">
-        <v>358.7628579284469</v>
+        <v>358.7685068626542</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27791,28 +27955,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4441484396729365</v>
+        <v>-0.448358470168832</v>
       </c>
       <c r="J5" t="n">
+        <v>329</v>
+      </c>
+      <c r="K5" t="n">
         <v>327</v>
       </c>
-      <c r="K5" t="n">
-        <v>325</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2257948608086094</v>
+        <v>0.2310566553305655</v>
       </c>
       <c r="M5" t="n">
-        <v>4.880292197834744</v>
+        <v>4.87192361525549</v>
       </c>
       <c r="N5" t="n">
-        <v>38.40459561466024</v>
+        <v>38.24709943289328</v>
       </c>
       <c r="O5" t="n">
-        <v>6.197144149901649</v>
+        <v>6.184423937028677</v>
       </c>
       <c r="P5" t="n">
-        <v>366.7365156390775</v>
+        <v>366.7815133243108</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27869,28 +28033,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3496929534722496</v>
+        <v>-0.348742810591451</v>
       </c>
       <c r="J6" t="n">
+        <v>329</v>
+      </c>
+      <c r="K6" t="n">
         <v>327</v>
       </c>
-      <c r="K6" t="n">
-        <v>325</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1831829751827884</v>
+        <v>0.1842990156001728</v>
       </c>
       <c r="M6" t="n">
-        <v>4.422498383603676</v>
+        <v>4.399622668040652</v>
       </c>
       <c r="N6" t="n">
-        <v>30.95981472943318</v>
+        <v>30.77445603231375</v>
       </c>
       <c r="O6" t="n">
-        <v>5.564154448740005</v>
+        <v>5.547472941106946</v>
       </c>
       <c r="P6" t="n">
-        <v>362.027404035646</v>
+        <v>362.0172507734187</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27947,28 +28111,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3662112133627405</v>
+        <v>-0.366267602003167</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09582772788520744</v>
+        <v>0.09699046568160929</v>
       </c>
       <c r="M7" t="n">
-        <v>6.491165783983242</v>
+        <v>6.452022532839239</v>
       </c>
       <c r="N7" t="n">
-        <v>71.6764899001605</v>
+        <v>71.24080169045513</v>
       </c>
       <c r="O7" t="n">
-        <v>8.466196897081977</v>
+        <v>8.440426629647055</v>
       </c>
       <c r="P7" t="n">
-        <v>341.8321683023154</v>
+        <v>341.8327717722738</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28025,28 +28189,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4524710336446606</v>
+        <v>-0.4515738257994587</v>
       </c>
       <c r="J8" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2086229975554876</v>
+        <v>0.2101105301930641</v>
       </c>
       <c r="M8" t="n">
-        <v>4.939710139558483</v>
+        <v>4.914074190424484</v>
       </c>
       <c r="N8" t="n">
-        <v>43.99023345273322</v>
+        <v>43.72648069755109</v>
       </c>
       <c r="O8" t="n">
-        <v>6.632513358654713</v>
+        <v>6.612600146504481</v>
       </c>
       <c r="P8" t="n">
-        <v>338.895994116929</v>
+        <v>338.8864123487625</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28103,28 +28267,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.451556350903722</v>
+        <v>-0.44916719265296</v>
       </c>
       <c r="J9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.227255315584491</v>
+        <v>0.2275702012681244</v>
       </c>
       <c r="M9" t="n">
-        <v>4.799615064030725</v>
+        <v>4.781677417105346</v>
       </c>
       <c r="N9" t="n">
-        <v>39.27347629916861</v>
+        <v>39.05963476565568</v>
       </c>
       <c r="O9" t="n">
-        <v>6.266855375638456</v>
+        <v>6.249770777049002</v>
       </c>
       <c r="P9" t="n">
-        <v>341.5741442687399</v>
+        <v>341.5486234394874</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28181,28 +28345,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.53563020755713</v>
+        <v>-0.5366566799225655</v>
       </c>
       <c r="J10" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K10" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3184528049863707</v>
+        <v>0.3220959801974471</v>
       </c>
       <c r="M10" t="n">
-        <v>4.575617405667268</v>
+        <v>4.552696526215607</v>
       </c>
       <c r="N10" t="n">
-        <v>34.78038927739696</v>
+        <v>34.57359020122252</v>
       </c>
       <c r="O10" t="n">
-        <v>5.897490082857025</v>
+        <v>5.879931139156522</v>
       </c>
       <c r="P10" t="n">
-        <v>345.7143345873906</v>
+        <v>345.7252985881365</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28259,28 +28423,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6469245812639257</v>
+        <v>-0.6432123899540453</v>
       </c>
       <c r="J11" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K11" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4564043106226618</v>
+        <v>0.4562534148033204</v>
       </c>
       <c r="M11" t="n">
-        <v>4.020129074511359</v>
+        <v>4.014769689372889</v>
       </c>
       <c r="N11" t="n">
-        <v>28.23495061653577</v>
+        <v>28.12339289426163</v>
       </c>
       <c r="O11" t="n">
-        <v>5.313656990861921</v>
+        <v>5.303149337352441</v>
       </c>
       <c r="P11" t="n">
-        <v>346.2359447621366</v>
+        <v>346.1962910873987</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28337,28 +28501,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6666654859104508</v>
+        <v>-0.660964174487401</v>
       </c>
       <c r="J12" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K12" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4458508258398806</v>
+        <v>0.4437165959460456</v>
       </c>
       <c r="M12" t="n">
-        <v>4.338550279226093</v>
+        <v>4.342103187795759</v>
       </c>
       <c r="N12" t="n">
-        <v>31.09862721387</v>
+        <v>31.04934029002648</v>
       </c>
       <c r="O12" t="n">
-        <v>5.576614314606131</v>
+        <v>5.572193490002522</v>
       </c>
       <c r="P12" t="n">
-        <v>350.4312284653547</v>
+        <v>350.3700243953844</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28415,28 +28579,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6825032015486743</v>
+        <v>-0.6771804114569667</v>
       </c>
       <c r="J13" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K13" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4220407664351912</v>
+        <v>0.4205740646503329</v>
       </c>
       <c r="M13" t="n">
-        <v>4.714617127327269</v>
+        <v>4.710355977397814</v>
       </c>
       <c r="N13" t="n">
-        <v>35.91206258718864</v>
+        <v>35.81544253614941</v>
       </c>
       <c r="O13" t="n">
-        <v>5.992667401682547</v>
+        <v>5.984600449165292</v>
       </c>
       <c r="P13" t="n">
-        <v>348.6866224353601</v>
+        <v>348.6294820943243</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28493,28 +28657,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6511864494076315</v>
+        <v>-0.6482342131117317</v>
       </c>
       <c r="J14" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K14" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4307603683539967</v>
+        <v>0.4314404888315907</v>
       </c>
       <c r="M14" t="n">
-        <v>4.342041684317139</v>
+        <v>4.329010201700314</v>
       </c>
       <c r="N14" t="n">
-        <v>31.54701400996027</v>
+        <v>31.39243708326848</v>
       </c>
       <c r="O14" t="n">
-        <v>5.616672859439142</v>
+        <v>5.602895419626221</v>
       </c>
       <c r="P14" t="n">
-        <v>341.6961132492679</v>
+        <v>341.664422350902</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28571,28 +28735,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6172769169177079</v>
+        <v>-0.6163891242574133</v>
       </c>
       <c r="J15" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K15" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3976183806449669</v>
+        <v>0.4000355677676639</v>
       </c>
       <c r="M15" t="n">
-        <v>4.540590681513996</v>
+        <v>4.51777044187722</v>
       </c>
       <c r="N15" t="n">
-        <v>32.49776493515044</v>
+        <v>32.30300596500012</v>
       </c>
       <c r="O15" t="n">
-        <v>5.700681093970302</v>
+        <v>5.683573344736577</v>
       </c>
       <c r="P15" t="n">
-        <v>336.4802767776235</v>
+        <v>336.4707455311793</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28649,28 +28813,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5830602879751351</v>
+        <v>-0.5776408721347657</v>
       </c>
       <c r="J16" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K16" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3314912401502534</v>
+        <v>0.3295134054371679</v>
       </c>
       <c r="M16" t="n">
-        <v>5.007352933439043</v>
+        <v>5.005599528527186</v>
       </c>
       <c r="N16" t="n">
-        <v>38.83429547737806</v>
+        <v>38.72588383059344</v>
       </c>
       <c r="O16" t="n">
-        <v>6.231716896440182</v>
+        <v>6.223012440176658</v>
       </c>
       <c r="P16" t="n">
-        <v>343.9601787709234</v>
+        <v>343.902282429807</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28727,28 +28891,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3733225379012092</v>
+        <v>-0.3672964719085929</v>
       </c>
       <c r="J17" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K17" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1721009350131261</v>
+        <v>0.1687521319837031</v>
       </c>
       <c r="M17" t="n">
-        <v>5.016164737806367</v>
+        <v>5.018727571917503</v>
       </c>
       <c r="N17" t="n">
-        <v>37.97659652144823</v>
+        <v>37.90384663382002</v>
       </c>
       <c r="O17" t="n">
-        <v>6.162515437826361</v>
+        <v>6.156609995266877</v>
       </c>
       <c r="P17" t="n">
-        <v>343.1778244868251</v>
+        <v>343.1134445814412</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28805,28 +28969,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3963547350169374</v>
+        <v>-0.3886996831615622</v>
       </c>
       <c r="J18" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K18" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2152257354765243</v>
+        <v>0.2095666356812924</v>
       </c>
       <c r="M18" t="n">
-        <v>4.652452949497109</v>
+        <v>4.6693715834051</v>
       </c>
       <c r="N18" t="n">
-        <v>32.44681799737642</v>
+        <v>32.50423820660836</v>
       </c>
       <c r="O18" t="n">
-        <v>5.696210845586426</v>
+        <v>5.701248828687304</v>
       </c>
       <c r="P18" t="n">
-        <v>341.1965785785278</v>
+        <v>341.1147997375597</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28883,28 +29047,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4639622829533094</v>
+        <v>-0.4549626784111908</v>
       </c>
       <c r="J19" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K19" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3465036485828491</v>
+        <v>0.3371843331075212</v>
       </c>
       <c r="M19" t="n">
-        <v>3.830129237119674</v>
+        <v>3.860335275668219</v>
       </c>
       <c r="N19" t="n">
-        <v>22.99609890063171</v>
+        <v>23.2084116184196</v>
       </c>
       <c r="O19" t="n">
-        <v>4.795424788340624</v>
+        <v>4.817510935993773</v>
       </c>
       <c r="P19" t="n">
-        <v>341.9659672984714</v>
+        <v>341.8698281867024</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28961,28 +29125,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3409282708356152</v>
+        <v>-0.3376618513215399</v>
       </c>
       <c r="J20" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K20" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2375448666773111</v>
+        <v>0.2360224763399185</v>
       </c>
       <c r="M20" t="n">
-        <v>3.728502753189932</v>
+        <v>3.720760586404384</v>
       </c>
       <c r="N20" t="n">
-        <v>21.132366474233</v>
+        <v>21.05036885944714</v>
       </c>
       <c r="O20" t="n">
-        <v>4.596995374615141</v>
+        <v>4.588068096644506</v>
       </c>
       <c r="P20" t="n">
-        <v>349.2273997032711</v>
+        <v>349.1925072163332</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29039,28 +29203,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.171475372768502</v>
+        <v>-0.1692822243449455</v>
       </c>
       <c r="J21" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K21" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05931826499439974</v>
+        <v>0.0585693123546428</v>
       </c>
       <c r="M21" t="n">
-        <v>3.873730211217965</v>
+        <v>3.864507130572552</v>
       </c>
       <c r="N21" t="n">
-        <v>26.412605334873</v>
+        <v>26.27298610980471</v>
       </c>
       <c r="O21" t="n">
-        <v>5.139319540062965</v>
+        <v>5.125718106744137</v>
       </c>
       <c r="P21" t="n">
-        <v>350.3171063727758</v>
+        <v>350.2936756943332</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29098,7 +29262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V328"/>
+  <dimension ref="A1:V330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65793,6 +65957,230 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:39+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-41.31742715323418,175.8627056190485</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-41.317878786129455,175.86201092269022</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-41.31837965444337,175.86141188001992</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-41.31887385310613,175.8608037574758</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-41.319413849737614,175.8602671858646</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-41.3197535818721,175.85945544578175</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-41.32014512952696,175.85873657653866</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-41.32058774239442,175.8580716155297</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-41.32095444323726,175.8573345616687</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-41.321309848769125,175.8565960652243</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-41.32162287642194,175.8558188045271</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-41.32185350451151,175.85497631015824</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-41.322037822422786,175.85410454043628</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-41.322233185713756,175.85326027926894</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-41.322516960386764,175.8524449406847</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>-41.322815965568644,175.85162142686661</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>-41.3231435123449,175.8508211556047</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>-41.32350863601387,175.85006743972255</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>-41.323872958279374,175.84931190644747</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>-41.324280903044084,175.84859632724823</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-41.31742715323418,175.8627056190485</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-41.31787655032801,175.86200717920633</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-41.3183789875888,175.86141090918554</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-41.31887273771329,175.860802037763</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-41.319412624881146,175.8602652760957</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-41.31975266715282,175.85945429598638</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-41.32014265298536,175.85873380440233</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-41.32058582055248,175.85806964214288</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-41.32095548719136,175.85733549798806</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-41.321306773807194,175.85659381859153</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-41.32161967543815,175.8558168925217</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-41.321850195106414,175.85497442864605</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-41.32203451300675,175.85410265894768</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-41.32223301654702,175.8532601975755</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-41.322518059772015,175.8524454724188</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>-41.32281957395791,175.85162386822873</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>-41.32314419699399,175.8508217301014</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>-41.32350641689466,175.85006561616046</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>-41.3238709818591,175.84931024372096</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>-41.324282154980835,175.84859749453025</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0349/nzd0349.xlsx
+++ b/data/nzd0349/nzd0349.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V330"/>
+  <dimension ref="A1:V334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24204,6 +24204,294 @@
         <v>347.67</v>
       </c>
       <c r="V330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>361.09</v>
+      </c>
+      <c r="C331" t="n">
+        <v>345.05</v>
+      </c>
+      <c r="D331" t="n">
+        <v>345.54</v>
+      </c>
+      <c r="E331" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="F331" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="G331" t="n">
+        <v>329.47</v>
+      </c>
+      <c r="H331" t="n">
+        <v>325.06</v>
+      </c>
+      <c r="I331" t="n">
+        <v>327.82</v>
+      </c>
+      <c r="J331" t="n">
+        <v>329.12</v>
+      </c>
+      <c r="K331" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="L331" t="n">
+        <v>334.49</v>
+      </c>
+      <c r="M331" t="n">
+        <v>332.01</v>
+      </c>
+      <c r="N331" t="n">
+        <v>324.16</v>
+      </c>
+      <c r="O331" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="P331" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="R331" t="n">
+        <v>335.73</v>
+      </c>
+      <c r="S331" t="n">
+        <v>334.79</v>
+      </c>
+      <c r="T331" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="U331" t="n">
+        <v>346.55</v>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="C332" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="D332" t="n">
+        <v>344.97</v>
+      </c>
+      <c r="E332" t="n">
+        <v>348.31</v>
+      </c>
+      <c r="F332" t="n">
+        <v>349.94</v>
+      </c>
+      <c r="G332" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="H332" t="n">
+        <v>324.36</v>
+      </c>
+      <c r="I332" t="n">
+        <v>326.64</v>
+      </c>
+      <c r="J332" t="n">
+        <v>328.36</v>
+      </c>
+      <c r="K332" t="n">
+        <v>329.19</v>
+      </c>
+      <c r="L332" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="M332" t="n">
+        <v>331.48</v>
+      </c>
+      <c r="N332" t="n">
+        <v>323.95</v>
+      </c>
+      <c r="O332" t="n">
+        <v>320.09</v>
+      </c>
+      <c r="P332" t="n">
+        <v>333.41</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="R332" t="n">
+        <v>335.47</v>
+      </c>
+      <c r="S332" t="n">
+        <v>333.8</v>
+      </c>
+      <c r="T332" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="U332" t="n">
+        <v>346.35</v>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="C333" t="n">
+        <v>345.47</v>
+      </c>
+      <c r="D333" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="E333" t="n">
+        <v>348.42</v>
+      </c>
+      <c r="F333" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="G333" t="n">
+        <v>327.13</v>
+      </c>
+      <c r="H333" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="I333" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="J333" t="n">
+        <v>327.89</v>
+      </c>
+      <c r="K333" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="L333" t="n">
+        <v>332.25</v>
+      </c>
+      <c r="M333" t="n">
+        <v>331.49</v>
+      </c>
+      <c r="N333" t="n">
+        <v>324.58</v>
+      </c>
+      <c r="O333" t="n">
+        <v>321.54</v>
+      </c>
+      <c r="P333" t="n">
+        <v>333.84</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>338.37</v>
+      </c>
+      <c r="R333" t="n">
+        <v>335.06</v>
+      </c>
+      <c r="S333" t="n">
+        <v>333.18</v>
+      </c>
+      <c r="T333" t="n">
+        <v>341.68</v>
+      </c>
+      <c r="U333" t="n">
+        <v>346.34</v>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:01:05+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>362.03</v>
+      </c>
+      <c r="C334" t="n">
+        <v>346.41</v>
+      </c>
+      <c r="D334" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="E334" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="F334" t="n">
+        <v>349.91</v>
+      </c>
+      <c r="G334" t="n">
+        <v>327.48</v>
+      </c>
+      <c r="H334" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="I334" t="n">
+        <v>326.05</v>
+      </c>
+      <c r="J334" t="n">
+        <v>327.53</v>
+      </c>
+      <c r="K334" t="n">
+        <v>328.49</v>
+      </c>
+      <c r="L334" t="n">
+        <v>331.78</v>
+      </c>
+      <c r="M334" t="n">
+        <v>331.33</v>
+      </c>
+      <c r="N334" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="O334" t="n">
+        <v>322.71</v>
+      </c>
+      <c r="P334" t="n">
+        <v>334.67</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>338.79</v>
+      </c>
+      <c r="R334" t="n">
+        <v>335.13</v>
+      </c>
+      <c r="S334" t="n">
+        <v>333.46</v>
+      </c>
+      <c r="T334" t="n">
+        <v>342.15</v>
+      </c>
+      <c r="U334" t="n">
+        <v>346.82</v>
+      </c>
+      <c r="V334" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24220,7 +24508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27553,6 +27841,46 @@
       </c>
       <c r="B333" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -27721,28 +28049,28 @@
         <v>0.0312</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3914144647597693</v>
+        <v>-0.3930702385144115</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K2" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2717775279248571</v>
+        <v>0.2784581097168255</v>
       </c>
       <c r="M2" t="n">
-        <v>3.641898587598087</v>
+        <v>3.607853925504639</v>
       </c>
       <c r="N2" t="n">
-        <v>23.47783227998589</v>
+        <v>23.20510933475241</v>
       </c>
       <c r="O2" t="n">
-        <v>4.84539289222101</v>
+        <v>4.817168186263835</v>
       </c>
       <c r="P2" t="n">
-        <v>372.4559041459983</v>
+        <v>372.4736335707858</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27799,28 +28127,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3412527208725835</v>
+        <v>-0.3492421948786027</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1746931339644026</v>
+        <v>0.1845736007526703</v>
       </c>
       <c r="M3" t="n">
-        <v>4.438606112659891</v>
+        <v>4.421235027982156</v>
       </c>
       <c r="N3" t="n">
-        <v>31.46484442988869</v>
+        <v>31.23274935863525</v>
       </c>
       <c r="O3" t="n">
-        <v>5.609353298722473</v>
+        <v>5.588626786486574</v>
       </c>
       <c r="P3" t="n">
-        <v>358.2280799602715</v>
+        <v>358.3136678488947</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27877,28 +28205,28 @@
         <v>0.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4020205160935634</v>
+        <v>-0.4072546686087149</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2244475235343523</v>
+        <v>0.2331446047037821</v>
       </c>
       <c r="M4" t="n">
-        <v>4.29732404206056</v>
+        <v>4.273290209549635</v>
       </c>
       <c r="N4" t="n">
-        <v>31.93938325468139</v>
+        <v>31.62000004468837</v>
       </c>
       <c r="O4" t="n">
-        <v>5.651493895836869</v>
+        <v>5.623166371777415</v>
       </c>
       <c r="P4" t="n">
-        <v>358.7685068626542</v>
+        <v>358.8245763042132</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27955,28 +28283,28 @@
         <v>0.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.448358470168832</v>
+        <v>-0.4621107597864275</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2310566553305655</v>
+        <v>0.2445872938149711</v>
       </c>
       <c r="M5" t="n">
-        <v>4.87192361525549</v>
+        <v>4.88237044395612</v>
       </c>
       <c r="N5" t="n">
-        <v>38.24709943289328</v>
+        <v>38.21158382716401</v>
       </c>
       <c r="O5" t="n">
-        <v>6.184423937028677</v>
+        <v>6.181551894723849</v>
       </c>
       <c r="P5" t="n">
-        <v>366.7815133243108</v>
+        <v>366.929057951557</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28033,28 +28361,28 @@
         <v>0.0358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.348742810591451</v>
+        <v>-0.3546343076981291</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1842990156001728</v>
+        <v>0.1929181170237096</v>
       </c>
       <c r="M6" t="n">
-        <v>4.399622668040652</v>
+        <v>4.381554826024541</v>
       </c>
       <c r="N6" t="n">
-        <v>30.77445603231375</v>
+        <v>30.48306015065832</v>
       </c>
       <c r="O6" t="n">
-        <v>5.547472941106946</v>
+        <v>5.521146633685644</v>
       </c>
       <c r="P6" t="n">
-        <v>362.0172507734187</v>
+        <v>362.0804710927829</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28111,28 +28439,28 @@
         <v>0.0496</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.366267602003167</v>
+        <v>-0.3752698643699734</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09699046568160929</v>
+        <v>0.1034247347385967</v>
       </c>
       <c r="M7" t="n">
-        <v>6.452022532839239</v>
+        <v>6.413579629442032</v>
       </c>
       <c r="N7" t="n">
-        <v>71.24080169045513</v>
+        <v>70.5755246058406</v>
       </c>
       <c r="O7" t="n">
-        <v>8.440426629647055</v>
+        <v>8.400924032857374</v>
       </c>
       <c r="P7" t="n">
-        <v>341.8327717722738</v>
+        <v>341.9293311229856</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28189,28 +28517,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4515738257994587</v>
+        <v>-0.4569678449297619</v>
       </c>
       <c r="J8" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K8" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2101105301930641</v>
+        <v>0.2181371550196936</v>
       </c>
       <c r="M8" t="n">
-        <v>4.914074190424484</v>
+        <v>4.884148076625544</v>
       </c>
       <c r="N8" t="n">
-        <v>43.72648069755109</v>
+        <v>43.26897532868676</v>
       </c>
       <c r="O8" t="n">
-        <v>6.612600146504481</v>
+        <v>6.577915728305339</v>
       </c>
       <c r="P8" t="n">
-        <v>338.8864123487625</v>
+        <v>338.9442659747276</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28267,28 +28595,28 @@
         <v>0.0558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.44916719265296</v>
+        <v>-0.4557393558326876</v>
       </c>
       <c r="J9" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K9" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2275702012681244</v>
+        <v>0.2368185996129859</v>
       </c>
       <c r="M9" t="n">
-        <v>4.781677417105346</v>
+        <v>4.761109904882138</v>
       </c>
       <c r="N9" t="n">
-        <v>39.05963476565568</v>
+        <v>38.69451735831842</v>
       </c>
       <c r="O9" t="n">
-        <v>6.249770777049002</v>
+        <v>6.220491729623826</v>
       </c>
       <c r="P9" t="n">
-        <v>341.5486234394874</v>
+        <v>341.6191210081486</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28345,28 +28673,28 @@
         <v>0.0568</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5366566799225655</v>
+        <v>-0.5435641626783271</v>
       </c>
       <c r="J10" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K10" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3220959801974471</v>
+        <v>0.3326354144103285</v>
       </c>
       <c r="M10" t="n">
-        <v>4.552696526215607</v>
+        <v>4.531098457112355</v>
       </c>
       <c r="N10" t="n">
-        <v>34.57359020122252</v>
+        <v>34.26894229230059</v>
       </c>
       <c r="O10" t="n">
-        <v>5.879931139156522</v>
+        <v>5.85396808090893</v>
       </c>
       <c r="P10" t="n">
-        <v>345.7252985881365</v>
+        <v>345.7993889743435</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28423,28 +28751,28 @@
         <v>0.0528</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6432123899540453</v>
+        <v>-0.6425929019433481</v>
       </c>
       <c r="J11" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K11" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4562534148033204</v>
+        <v>0.4620720559550952</v>
       </c>
       <c r="M11" t="n">
-        <v>4.014769689372889</v>
+        <v>3.972065353253366</v>
       </c>
       <c r="N11" t="n">
-        <v>28.12339289426163</v>
+        <v>27.79013427528114</v>
       </c>
       <c r="O11" t="n">
-        <v>5.303149337352441</v>
+        <v>5.271634876893613</v>
       </c>
       <c r="P11" t="n">
-        <v>346.1962910873987</v>
+        <v>346.1896622221907</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28501,28 +28829,28 @@
         <v>0.0492</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.660964174487401</v>
+        <v>-0.6600845299116883</v>
       </c>
       <c r="J12" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K12" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4437165959460456</v>
+        <v>0.449262553080605</v>
       </c>
       <c r="M12" t="n">
-        <v>4.342103187795759</v>
+        <v>4.300875902712286</v>
       </c>
       <c r="N12" t="n">
-        <v>31.04934029002648</v>
+        <v>30.68956623448672</v>
       </c>
       <c r="O12" t="n">
-        <v>5.572193490002522</v>
+        <v>5.539816444114978</v>
       </c>
       <c r="P12" t="n">
-        <v>350.3700243953844</v>
+        <v>350.3605718433864</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28579,28 +28907,28 @@
         <v>0.0485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6771804114569667</v>
+        <v>-0.6744376653668664</v>
       </c>
       <c r="J13" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K13" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4205740646503329</v>
+        <v>0.4247130146107221</v>
       </c>
       <c r="M13" t="n">
-        <v>4.710355977397814</v>
+        <v>4.666121003420953</v>
       </c>
       <c r="N13" t="n">
-        <v>35.81544253614941</v>
+        <v>35.40135356039301</v>
       </c>
       <c r="O13" t="n">
-        <v>5.984600449165292</v>
+        <v>5.949903659757275</v>
       </c>
       <c r="P13" t="n">
-        <v>348.6294820943243</v>
+        <v>348.5999300160205</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28657,28 +28985,28 @@
         <v>0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6482342131117317</v>
+        <v>-0.6473900992190694</v>
       </c>
       <c r="J14" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K14" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4314404888315907</v>
+        <v>0.437032143612487</v>
       </c>
       <c r="M14" t="n">
-        <v>4.329010201700314</v>
+        <v>4.282608074847801</v>
       </c>
       <c r="N14" t="n">
-        <v>31.39243708326848</v>
+        <v>31.02055616059832</v>
       </c>
       <c r="O14" t="n">
-        <v>5.602895419626221</v>
+        <v>5.569610054626654</v>
       </c>
       <c r="P14" t="n">
-        <v>341.664422350902</v>
+        <v>341.6553105646486</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28735,28 +29063,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6163891242574133</v>
+        <v>-0.6138243309257976</v>
       </c>
       <c r="J15" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K15" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4000355677676639</v>
+        <v>0.4039264732281551</v>
       </c>
       <c r="M15" t="n">
-        <v>4.51777044187722</v>
+        <v>4.479250748589632</v>
       </c>
       <c r="N15" t="n">
-        <v>32.30300596500012</v>
+        <v>31.94721243443477</v>
       </c>
       <c r="O15" t="n">
-        <v>5.683573344736577</v>
+        <v>5.652186518015376</v>
       </c>
       <c r="P15" t="n">
-        <v>336.4707455311793</v>
+        <v>336.4430720648583</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28813,28 +29141,28 @@
         <v>0.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5776408721347657</v>
+        <v>-0.5658716663714944</v>
       </c>
       <c r="J16" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K16" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3295134054371679</v>
+        <v>0.324237293599352</v>
       </c>
       <c r="M16" t="n">
-        <v>5.005599528527186</v>
+        <v>5.008738414971067</v>
       </c>
       <c r="N16" t="n">
-        <v>38.72588383059344</v>
+        <v>38.58082850524274</v>
       </c>
       <c r="O16" t="n">
-        <v>6.223012440176658</v>
+        <v>6.211346754548705</v>
       </c>
       <c r="P16" t="n">
-        <v>343.902282429807</v>
+        <v>343.7760460728039</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28891,28 +29219,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3672964719085929</v>
+        <v>-0.3562129835318313</v>
       </c>
       <c r="J17" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K17" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1687521319837031</v>
+        <v>0.1627837566805855</v>
       </c>
       <c r="M17" t="n">
-        <v>5.018727571917503</v>
+        <v>5.019774460730127</v>
       </c>
       <c r="N17" t="n">
-        <v>37.90384663382002</v>
+        <v>37.72684307613797</v>
       </c>
       <c r="O17" t="n">
-        <v>6.156609995266877</v>
+        <v>6.14221809089664</v>
       </c>
       <c r="P17" t="n">
-        <v>343.1134445814412</v>
+        <v>342.9945715887426</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28969,28 +29297,28 @@
         <v>0.0626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3886996831615622</v>
+        <v>-0.3779891135111995</v>
       </c>
       <c r="J18" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K18" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2095666356812924</v>
+        <v>0.2032856888173656</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6693715834051</v>
+        <v>4.675400442102868</v>
       </c>
       <c r="N18" t="n">
-        <v>32.50423820660836</v>
+        <v>32.37119957408045</v>
       </c>
       <c r="O18" t="n">
-        <v>5.701248828687304</v>
+        <v>5.689569366312397</v>
       </c>
       <c r="P18" t="n">
-        <v>341.1147997375597</v>
+        <v>340.9999471400083</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29047,28 +29375,28 @@
         <v>0.0596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4549626784111908</v>
+        <v>-0.4454135731558807</v>
       </c>
       <c r="J19" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K19" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3371843331075212</v>
+        <v>0.3314102579161468</v>
       </c>
       <c r="M19" t="n">
-        <v>3.860335275668219</v>
+        <v>3.870435734851163</v>
       </c>
       <c r="N19" t="n">
-        <v>23.2084116184196</v>
+        <v>23.13795934509918</v>
       </c>
       <c r="O19" t="n">
-        <v>4.817510935993773</v>
+        <v>4.810193275233249</v>
       </c>
       <c r="P19" t="n">
-        <v>341.8698281867024</v>
+        <v>341.7674382170763</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29125,28 +29453,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3376618513215399</v>
+        <v>-0.3339210312122203</v>
       </c>
       <c r="J20" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K20" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2360224763399185</v>
+        <v>0.2363291986337757</v>
       </c>
       <c r="M20" t="n">
-        <v>3.720760586404384</v>
+        <v>3.692928036829438</v>
       </c>
       <c r="N20" t="n">
-        <v>21.05036885944714</v>
+        <v>20.82959117942394</v>
       </c>
       <c r="O20" t="n">
-        <v>4.588068096644506</v>
+        <v>4.563944695044402</v>
       </c>
       <c r="P20" t="n">
-        <v>349.1925072163332</v>
+        <v>349.1523846677377</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29203,28 +29531,28 @@
         <v>0.0574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1692822243449455</v>
+        <v>-0.1675026807081627</v>
       </c>
       <c r="J21" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K21" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0585693123546428</v>
+        <v>0.05879555367424771</v>
       </c>
       <c r="M21" t="n">
-        <v>3.864507130572552</v>
+        <v>3.829538938169392</v>
       </c>
       <c r="N21" t="n">
-        <v>26.27298610980471</v>
+        <v>25.96494495644663</v>
       </c>
       <c r="O21" t="n">
-        <v>5.125718106744137</v>
+        <v>5.09558092433499</v>
       </c>
       <c r="P21" t="n">
-        <v>350.2936756943332</v>
+        <v>350.2745895296094</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29262,7 +29590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V330"/>
+  <dimension ref="A1:V334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66181,6 +66509,454 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-41.31741525340701,175.86268417712552</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-41.31786240888087,175.8619835016767</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-41.31836728732074,175.8613938754579</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-41.318857944079255,175.86077922894606</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-41.319397693294874,175.86024199510933</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-41.3197369209118,175.8594345030856</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-41.320127037013,175.8587163245476</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-41.3205606942451,175.85804384194805</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-41.32094504765013,175.85732613479593</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-41.32129258167457,175.85658344951995</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-41.32159767893319,175.85580375361775</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-41.321828187561444,175.8549619165952</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-41.3220150701868,175.8540916052062</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-41.32222388154298,175.85325578613126</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-41.3225106177794,175.85244187298835</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>-41.322810031772846,175.85161741218286</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>-41.32313354689657,175.85081279348793</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>-41.32348919958928,175.85005146783828</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>-41.32386140382203,175.84930218589406</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>-41.3242739069267,175.84858980420245</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-41.317411731484256,175.862677831087</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-41.31786285604134,175.86198425037313</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-41.31836383180064,175.86138884477265</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-41.31885624163693,175.86077660412255</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-41.31939279386702,175.860234356038</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-41.31972698967072,175.8594220196012</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-41.32012222151431,175.85871093428574</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-41.3205522950814,175.85803521752476</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-41.320939380470215,175.85732105192142</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-41.32128595867896,175.85657861062148</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-41.3215875014452,175.8557976744265</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-41.32182380259928,175.8549594235936</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-41.32201333274326,175.85409061742538</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-41.32222836446166,175.85325795100653</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-41.32252161163208,175.8524471903291</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>-41.32281428165364,175.8516202875644</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>-41.32313156902126,175.85081113383146</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>-41.32348162397427,175.85004524257891</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>-41.32386269609692,175.84930327306103</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>-41.32427243405982,175.84858843092982</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-41.31741568030673,175.86268494634234</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-41.31786475647325,175.86198743233308</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-41.31836704482811,175.8613935224273</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-41.31885688739092,175.86077759974526</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-41.31939016917329,175.86023026367883</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-41.31972163202689,175.8594152850915</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-41.320117681186716,175.85870585203955</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-41.32054560422167,175.8580283472231</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-41.32093587576673,175.8573179085653</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-41.3212831202522,175.85657653680818</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-41.3215792937933,175.85579277185434</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-41.32182388533442,175.8549594706314</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-41.32201854507389,175.85409358076802</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-41.32224062905023,175.85326387378007</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-41.322525248060195,175.85244894914217</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>-41.32281837116149,175.85162305444135</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>-41.323128450063955,175.8508085166811</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>-41.32347687964953,175.8500413439324</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>-41.3238630001616,175.84930352886502</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>-41.32427236041647,175.8485883622662</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:01:05+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-41.31742026947817,175.86269321542397</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-41.31787001060805,175.86199622951744</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-41.31837322838983,175.86140252470742</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-41.31886199471763,175.86078547421636</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-41.319392618887434,175.86023408321407</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-41.319723918826135,175.85941815957722</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-41.32012160237875,175.8587102412521</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-41.320548095499284,175.85803090531397</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-41.32093319131294,175.85731550088852</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-41.32128043951576,175.85657457820687</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-41.32157543619682,175.85579046764587</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-41.32182256157223,175.8549587180272</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-41.32202657040814,175.8540981433759</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-41.322250525304156,175.8532686528473</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-41.32253226721205,175.85245234406108</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>-41.32282173899143,175.85162533304612</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>-41.323128982568875,175.85080896351167</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>-41.32347902224781,175.85004310461142</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>-41.32386657292148,175.84930653456223</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>-41.32427589529694,175.84859165812057</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
